--- a/Datas/GameTimeEventData.xlsx
+++ b/Datas/GameTimeEventData.xlsx
@@ -18,6 +18,41 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>作者</author>
+  </authors>
+  <commentList>
+    <comment ref="C3" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>时间序列, 0
+苏醒序列  1</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
   <si>
@@ -65,7 +100,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -79,6 +114,19 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -385,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:G4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -448,7 +496,7 @@
         <v>10</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
@@ -467,5 +515,6 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>